--- a/dados/excel/genero_por_secretaria.xlsx
+++ b/dados/excel/genero_por_secretaria.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadados" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$H$82</definedName>
@@ -646,7 +646,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>10/10/2026 14:55</t>
+          <t>12/10/2026 16:30</t>
         </is>
       </c>
     </row>

--- a/dados/excel/genero_por_secretaria.xlsx
+++ b/dados/excel/genero_por_secretaria.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>12/10/2026 16:30</t>
+          <t>16/10/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -892,22 +892,22 @@
         </is>
       </c>
       <c r="C2" s="10" t="n">
-        <v>2201</v>
+        <v>2173</v>
       </c>
       <c r="D2" s="10" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E2" s="11" t="n">
-        <v>8948253.720000001</v>
+        <v>8846144.01</v>
       </c>
       <c r="F2" s="11" t="n">
-        <v>4065.540081781009</v>
+        <v>4070.936037735849</v>
       </c>
       <c r="G2" s="12" t="n">
         <v>197</v>
       </c>
       <c r="H2" s="13" t="n">
-        <v>85.79000000000001</v>
+        <v>84.77</v>
       </c>
     </row>
     <row r="3">
@@ -937,7 +937,7 @@
         <v>197</v>
       </c>
       <c r="H3" s="19" t="n">
-        <v>85.79000000000001</v>
+        <v>84.77</v>
       </c>
     </row>
     <row r="4">
@@ -952,22 +952,22 @@
         </is>
       </c>
       <c r="C4" s="10" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" s="11" t="n">
-        <v>108315.53</v>
+        <v>210425.24</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>3868.411785714286</v>
+        <v>3757.593571428571</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>197</v>
       </c>
       <c r="H4" s="13" t="n">
-        <v>85.79000000000001</v>
+        <v>84.77</v>
       </c>
     </row>
     <row r="5">
@@ -982,22 +982,22 @@
         </is>
       </c>
       <c r="C5" s="16" t="n">
-        <v>8317</v>
+        <v>8159</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>36680963.84</v>
+        <v>35756893.29</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>4410.359966334016</v>
+        <v>4382.509289128569</v>
       </c>
       <c r="G5" s="18" t="n">
         <v>297</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>69.02</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1027,7 +1027,7 @@
         <v>297</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>69.02</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1042,22 +1042,22 @@
         </is>
       </c>
       <c r="C7" s="16" t="n">
-        <v>151</v>
+        <v>309</v>
       </c>
       <c r="D7" s="16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>994740.0599999999</v>
+        <v>1918810.61</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>6587.682516556291</v>
+        <v>6209.743074433657</v>
       </c>
       <c r="G7" s="18" t="n">
         <v>297</v>
       </c>
       <c r="H7" s="19" t="n">
-        <v>69.02</v>
+        <v>67.68000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1162,22 +1162,22 @@
         </is>
       </c>
       <c r="C11" s="16" t="n">
-        <v>446428</v>
+        <v>444146</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>15944</v>
+        <v>15860</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>2458493083.55</v>
+        <v>2447116268.17</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>5507.031556152392</v>
+        <v>5509.711374570525</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>17797</v>
       </c>
       <c r="H11" s="19" t="n">
-        <v>89.59</v>
+        <v>89.12</v>
       </c>
     </row>
     <row r="12">
@@ -1192,22 +1192,22 @@
         </is>
       </c>
       <c r="C12" s="10" t="n">
-        <v>46152</v>
+        <v>45477</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>1661</v>
+        <v>1632</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>249775420.3</v>
+        <v>245785114.13</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>5412.017253856821</v>
+        <v>5404.602637157244</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>17797</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>89.59</v>
+        <v>89.12</v>
       </c>
     </row>
     <row r="13">
@@ -1222,22 +1222,22 @@
         </is>
       </c>
       <c r="C13" s="16" t="n">
-        <v>6005</v>
+        <v>8962</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>192</v>
+        <v>305</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>32947751.44</v>
+        <v>48314872.99</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>5486.719640299751</v>
+        <v>5391.081565498773</v>
       </c>
       <c r="G13" s="18" t="n">
         <v>17797</v>
       </c>
       <c r="H13" s="19" t="n">
-        <v>89.59</v>
+        <v>89.12</v>
       </c>
     </row>
     <row r="14">
@@ -1252,22 +1252,22 @@
         </is>
       </c>
       <c r="C14" s="10" t="n">
-        <v>7258</v>
+        <v>7164</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E14" s="11" t="n">
-        <v>51677735.24</v>
+        <v>50872664.85</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>7120.106811793883</v>
+        <v>7101.153664154104</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>304</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>59.54</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="15">
@@ -1297,7 +1297,7 @@
         <v>304</v>
       </c>
       <c r="H15" s="19" t="n">
-        <v>59.54</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="16">
@@ -1312,22 +1312,22 @@
         </is>
       </c>
       <c r="C16" s="10" t="n">
-        <v>261</v>
+        <v>355</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>3373786.36</v>
+        <v>4178856.75</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12926.3845210728</v>
+        <v>11771.42746478873</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>304</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>59.54</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="17">
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="C21" s="16" t="n">
-        <v>126373</v>
+        <v>125887</v>
       </c>
       <c r="D21" s="16" t="n">
-        <v>2644</v>
+        <v>2632</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>1062531888.05</v>
+        <v>1056496419.87</v>
       </c>
       <c r="F21" s="17" t="n">
-        <v>8407.902701130779</v>
+        <v>8392.418755471177</v>
       </c>
       <c r="G21" s="18" t="n">
         <v>3977</v>
       </c>
       <c r="H21" s="19" t="n">
-        <v>66.48</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1492,22 +1492,22 @@
         </is>
       </c>
       <c r="C22" s="10" t="n">
-        <v>56089</v>
+        <v>55759</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>1272</v>
+        <v>1266</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>639677396.27</v>
+        <v>636854228.8</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>11404.68534418513</v>
+        <v>11421.55040083215</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>3977</v>
       </c>
       <c r="H22" s="13" t="n">
-        <v>66.48</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1522,22 +1522,22 @@
         </is>
       </c>
       <c r="C23" s="16" t="n">
-        <v>3238</v>
+        <v>4054</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>34916377.44</v>
+        <v>43775013.09</v>
       </c>
       <c r="F23" s="17" t="n">
-        <v>10783.31607164917</v>
+        <v>10797.9805352738</v>
       </c>
       <c r="G23" s="18" t="n">
         <v>3977</v>
       </c>
       <c r="H23" s="19" t="n">
-        <v>66.48</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1552,22 +1552,22 @@
         </is>
       </c>
       <c r="C24" s="10" t="n">
-        <v>8972</v>
+        <v>8901</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>61217402.78</v>
+        <v>60678882.7</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>6823.161255015604</v>
+        <v>6817.086024042243</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>585</v>
       </c>
       <c r="H24" s="13" t="n">
-        <v>44.27</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="25">
@@ -1582,22 +1582,22 @@
         </is>
       </c>
       <c r="C25" s="16" t="n">
-        <v>7093</v>
+        <v>7091</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>50510458.56</v>
+        <v>50490994.56</v>
       </c>
       <c r="F25" s="17" t="n">
-        <v>7121.169964753984</v>
+        <v>7120.433586236074</v>
       </c>
       <c r="G25" s="18" t="n">
         <v>585</v>
       </c>
       <c r="H25" s="19" t="n">
-        <v>44.27</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="26">
@@ -1612,22 +1612,22 @@
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>328</v>
+        <v>401</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>1679175.13</v>
+        <v>2237159.21</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5119.43637195122</v>
+        <v>5578.950648379052</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>585</v>
       </c>
       <c r="H26" s="13" t="n">
-        <v>44.27</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="27">
@@ -1642,22 +1642,22 @@
         </is>
       </c>
       <c r="C27" s="16" t="n">
-        <v>5135</v>
+        <v>5105</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>62625762.01</v>
+        <v>62563255.08</v>
       </c>
       <c r="F27" s="17" t="n">
-        <v>12195.86407205453</v>
+        <v>12255.28992752204</v>
       </c>
       <c r="G27" s="18" t="n">
         <v>298</v>
       </c>
       <c r="H27" s="19" t="n">
-        <v>56.04</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="28">
@@ -1672,22 +1672,22 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>3845</v>
+        <v>3843</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>66432235.11</v>
+        <v>66317875.69</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>17277.56439791938</v>
+        <v>17256.79825396825</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>298</v>
       </c>
       <c r="H28" s="13" t="n">
-        <v>56.04</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="29">
@@ -1702,22 +1702,22 @@
         </is>
       </c>
       <c r="C29" s="16" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>541358.15</v>
+        <v>718224.5</v>
       </c>
       <c r="F29" s="17" t="n">
-        <v>5107.152358490566</v>
+        <v>5204.525362318841</v>
       </c>
       <c r="G29" s="18" t="n">
         <v>298</v>
       </c>
       <c r="H29" s="19" t="n">
-        <v>56.04</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="30">
@@ -1927,7 +1927,7 @@
         <v>251</v>
       </c>
       <c r="H36" s="13" t="n">
-        <v>45.02</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="37">
@@ -1942,22 +1942,22 @@
         </is>
       </c>
       <c r="C37" s="16" t="n">
-        <v>2283</v>
+        <v>2255</v>
       </c>
       <c r="D37" s="16" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>14525232.8</v>
+        <v>14348716.48</v>
       </c>
       <c r="F37" s="17" t="n">
-        <v>6362.344634253176</v>
+        <v>6363.067175166298</v>
       </c>
       <c r="G37" s="18" t="n">
         <v>251</v>
       </c>
       <c r="H37" s="19" t="n">
-        <v>45.02</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="38">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="C38" s="10" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="D38" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E38" s="11" t="n">
-        <v>495568.28</v>
+        <v>672084.6</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5445.805274725274</v>
+        <v>5647.769747899159</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>251</v>
       </c>
       <c r="H38" s="13" t="n">
-        <v>45.02</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="39">
@@ -2062,22 +2062,22 @@
         </is>
       </c>
       <c r="C41" s="16" t="n">
-        <v>4357</v>
+        <v>4287</v>
       </c>
       <c r="D41" s="16" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E41" s="17" t="n">
-        <v>39921827.76</v>
+        <v>39014544.92</v>
       </c>
       <c r="F41" s="17" t="n">
-        <v>9162.687114987377</v>
+        <v>9100.663615581992</v>
       </c>
       <c r="G41" s="18" t="n">
         <v>207</v>
       </c>
       <c r="H41" s="19" t="n">
-        <v>30.92</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="42">
@@ -2092,22 +2092,22 @@
         </is>
       </c>
       <c r="C42" s="10" t="n">
-        <v>1540</v>
+        <v>1451</v>
       </c>
       <c r="D42" s="10" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E42" s="11" t="n">
-        <v>10831492.68</v>
+        <v>10032731.99</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>7033.436805194805</v>
+        <v>6914.356988283942</v>
       </c>
       <c r="G42" s="12" t="n">
         <v>207</v>
       </c>
       <c r="H42" s="13" t="n">
-        <v>30.92</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="43">
@@ -2122,22 +2122,22 @@
         </is>
       </c>
       <c r="C43" s="16" t="n">
-        <v>81</v>
+        <v>240</v>
       </c>
       <c r="D43" s="16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E43" s="17" t="n">
-        <v>595161.4299999999</v>
+        <v>2301204.96</v>
       </c>
       <c r="F43" s="17" t="n">
-        <v>7347.671975308641</v>
+        <v>9588.353999999999</v>
       </c>
       <c r="G43" s="18" t="n">
         <v>207</v>
       </c>
       <c r="H43" s="19" t="n">
-        <v>30.92</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="44">
@@ -2152,16 +2152,16 @@
         </is>
       </c>
       <c r="C44" s="10" t="n">
-        <v>3257</v>
+        <v>3181</v>
       </c>
       <c r="D44" s="10" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E44" s="11" t="n">
-        <v>35649982.13</v>
+        <v>34322850.07</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>10945.65002456248</v>
+        <v>10789.95601068846</v>
       </c>
       <c r="G44" s="12" t="n">
         <v>341</v>
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="C46" s="10" t="n">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="D46" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" s="11" t="n">
-        <v>579872.61</v>
+        <v>1907004.67</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>17571.89727272727</v>
+        <v>17495.45568807339</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>341</v>
@@ -2242,22 +2242,22 @@
         </is>
       </c>
       <c r="C47" s="16" t="n">
-        <v>4565</v>
+        <v>4496</v>
       </c>
       <c r="D47" s="16" t="n">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E47" s="17" t="n">
-        <v>47040298.18</v>
+        <v>46765303.79</v>
       </c>
       <c r="F47" s="17" t="n">
-        <v>10304.55600876232</v>
+        <v>10401.53554048043</v>
       </c>
       <c r="G47" s="18" t="n">
         <v>515</v>
       </c>
       <c r="H47" s="19" t="n">
-        <v>59.81</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="48">
@@ -2272,22 +2272,22 @@
         </is>
       </c>
       <c r="C48" s="10" t="n">
-        <v>3060</v>
+        <v>3048</v>
       </c>
       <c r="D48" s="10" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E48" s="11" t="n">
-        <v>31097873.32</v>
+        <v>31085136.68</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>10162.70369934641</v>
+        <v>10198.53565616798</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>515</v>
       </c>
       <c r="H48" s="13" t="n">
-        <v>59.81</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="49">
@@ -2302,22 +2302,22 @@
         </is>
       </c>
       <c r="C49" s="16" t="n">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="D49" s="16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>337923.81</v>
+        <v>625654.84</v>
       </c>
       <c r="F49" s="17" t="n">
-        <v>5928.487894736842</v>
+        <v>4533.730724637681</v>
       </c>
       <c r="G49" s="18" t="n">
         <v>515</v>
       </c>
       <c r="H49" s="19" t="n">
-        <v>59.81</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="50">
@@ -2542,22 +2542,22 @@
         </is>
       </c>
       <c r="C57" s="16" t="n">
-        <v>5948</v>
+        <v>5944</v>
       </c>
       <c r="D57" s="16" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E57" s="17" t="n">
-        <v>53849287.84</v>
+        <v>53814866.37</v>
       </c>
       <c r="F57" s="17" t="n">
-        <v>9053.343618022865</v>
+        <v>9053.645082436069</v>
       </c>
       <c r="G57" s="18" t="n">
         <v>379</v>
       </c>
       <c r="H57" s="19" t="n">
-        <v>49.34</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="58">
@@ -2572,22 +2572,22 @@
         </is>
       </c>
       <c r="C58" s="10" t="n">
-        <v>4572</v>
+        <v>4506</v>
       </c>
       <c r="D58" s="10" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E58" s="11" t="n">
-        <v>26736591.65</v>
+        <v>26430603.33</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>5847.898436132983</v>
+        <v>5865.64654460719</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>379</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>49.34</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="59">
@@ -2602,22 +2602,22 @@
         </is>
       </c>
       <c r="C59" s="16" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D59" s="16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E59" s="17" t="n">
-        <v>203793.23</v>
+        <v>544203.02</v>
       </c>
       <c r="F59" s="17" t="n">
-        <v>10189.6615</v>
+        <v>6046.700222222223</v>
       </c>
       <c r="G59" s="18" t="n">
         <v>379</v>
       </c>
       <c r="H59" s="19" t="n">
-        <v>49.34</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="60">
@@ -2632,22 +2632,22 @@
         </is>
       </c>
       <c r="C60" s="10" t="n">
-        <v>5555</v>
+        <v>5529</v>
       </c>
       <c r="D60" s="10" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E60" s="11" t="n">
-        <v>37597381.4</v>
+        <v>37514920.66</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>6768.205472547254</v>
+        <v>6785.118585639356</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>291</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>67.7</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2662,22 +2662,22 @@
         </is>
       </c>
       <c r="C61" s="16" t="n">
-        <v>2741</v>
+        <v>2722</v>
       </c>
       <c r="D61" s="16" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E61" s="17" t="n">
-        <v>22561227.29</v>
+        <v>22453432.13</v>
       </c>
       <c r="F61" s="17" t="n">
-        <v>8231.020536300621</v>
+        <v>8248.87293534166</v>
       </c>
       <c r="G61" s="18" t="n">
         <v>291</v>
       </c>
       <c r="H61" s="19" t="n">
-        <v>67.7</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2692,22 +2692,22 @@
         </is>
       </c>
       <c r="C62" s="10" t="n">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="D62" s="10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E62" s="11" t="n">
-        <v>1471893.88</v>
+        <v>1662149.78</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>7587.081855670102</v>
+        <v>6954.601589958159</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>291</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>67.7</v>
+        <v>67.34999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2902,22 +2902,22 @@
         </is>
       </c>
       <c r="C69" s="16" t="n">
-        <v>23761</v>
+        <v>23654</v>
       </c>
       <c r="D69" s="16" t="n">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>240518340.12</v>
+        <v>239651399.77</v>
       </c>
       <c r="F69" s="17" t="n">
-        <v>10122.39973570136</v>
+        <v>10131.53799653336</v>
       </c>
       <c r="G69" s="18" t="n">
         <v>803</v>
       </c>
       <c r="H69" s="19" t="n">
-        <v>22.79</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="70">
@@ -2932,22 +2932,22 @@
         </is>
       </c>
       <c r="C70" s="10" t="n">
-        <v>4595</v>
+        <v>4514</v>
       </c>
       <c r="D70" s="10" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E70" s="11" t="n">
-        <v>39060888.8</v>
+        <v>38470878.05</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>8500.737497279652</v>
+        <v>8522.569350908285</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>803</v>
       </c>
       <c r="H70" s="13" t="n">
-        <v>22.79</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="71">
@@ -2962,22 +2962,22 @@
         </is>
       </c>
       <c r="C71" s="16" t="n">
-        <v>261</v>
+        <v>449</v>
       </c>
       <c r="D71" s="16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>2217597.71</v>
+        <v>3674548.81</v>
       </c>
       <c r="F71" s="17" t="n">
-        <v>8496.542950191571</v>
+        <v>8183.850356347439</v>
       </c>
       <c r="G71" s="18" t="n">
         <v>803</v>
       </c>
       <c r="H71" s="19" t="n">
-        <v>22.79</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="72">
@@ -2992,22 +2992,22 @@
         </is>
       </c>
       <c r="C72" s="10" t="n">
-        <v>7274</v>
+        <v>7272</v>
       </c>
       <c r="D72" s="10" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E72" s="11" t="n">
-        <v>58719192.8</v>
+        <v>58687681.78</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>8072.476326642837</v>
+        <v>8070.363281078108</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>278</v>
       </c>
       <c r="H72" s="13" t="n">
-        <v>26.62</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="73">
@@ -3022,22 +3022,22 @@
         </is>
       </c>
       <c r="C73" s="16" t="n">
-        <v>2650</v>
+        <v>2574</v>
       </c>
       <c r="D73" s="16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E73" s="17" t="n">
-        <v>18545590.13</v>
+        <v>18232281.07</v>
       </c>
       <c r="F73" s="17" t="n">
-        <v>6998.335898113207</v>
+        <v>7083.248278943279</v>
       </c>
       <c r="G73" s="18" t="n">
         <v>278</v>
       </c>
       <c r="H73" s="19" t="n">
-        <v>26.62</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="74">
@@ -3052,22 +3052,22 @@
         </is>
       </c>
       <c r="C74" s="10" t="n">
-        <v>171</v>
+        <v>249</v>
       </c>
       <c r="D74" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E74" s="11" t="n">
-        <v>986194.28</v>
+        <v>1331014.36</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>5767.218011695906</v>
+        <v>5345.439196787149</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>278</v>
       </c>
       <c r="H74" s="13" t="n">
-        <v>26.62</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="75">
@@ -3142,22 +3142,22 @@
         </is>
       </c>
       <c r="C77" s="16" t="n">
-        <v>1442</v>
+        <v>1429</v>
       </c>
       <c r="D77" s="16" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>10970178.09</v>
+        <v>10890585.25</v>
       </c>
       <c r="F77" s="17" t="n">
-        <v>7607.613099861303</v>
+        <v>7621.123337998601</v>
       </c>
       <c r="G77" s="18" t="n">
         <v>228</v>
       </c>
       <c r="H77" s="19" t="n">
-        <v>42.54</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="78">
@@ -3172,22 +3172,22 @@
         </is>
       </c>
       <c r="C78" s="10" t="n">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="D78" s="10" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E78" s="11" t="n">
-        <v>4640863.34</v>
+        <v>4583668.63</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>4554.331050049068</v>
+        <v>4551.805988083416</v>
       </c>
       <c r="G78" s="12" t="n">
         <v>228</v>
       </c>
       <c r="H78" s="13" t="n">
-        <v>42.54</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="79">
@@ -3202,22 +3202,22 @@
         </is>
       </c>
       <c r="C79" s="16" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D79" s="16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>9000.540000000001</v>
+        <v>145788.09</v>
       </c>
       <c r="F79" s="17" t="n">
-        <v>4500.27</v>
+        <v>5399.558888888889</v>
       </c>
       <c r="G79" s="18" t="n">
         <v>228</v>
       </c>
       <c r="H79" s="19" t="n">
-        <v>42.54</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="80">
@@ -3262,16 +3262,16 @@
         </is>
       </c>
       <c r="C81" s="16" t="n">
-        <v>4431</v>
+        <v>4422</v>
       </c>
       <c r="D81" s="16" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E81" s="17" t="n">
-        <v>39892325.68</v>
+        <v>39883336.56</v>
       </c>
       <c r="F81" s="17" t="n">
-        <v>9003.007375310313</v>
+        <v>9019.298181818182</v>
       </c>
       <c r="G81" s="18" t="n">
         <v>338</v>
@@ -3292,16 +3292,16 @@
         </is>
       </c>
       <c r="C82" s="10" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D82" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E82" s="11" t="n">
-        <v>672919.3</v>
+        <v>681908.42</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>6662.567326732674</v>
+        <v>6199.167454545455</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>338</v>
